--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F183271D-7D76-41B7-AF00-2421524F0BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF14A68A-B8C9-4652-B108-7BC76F1DEDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -304,454 +304,454 @@
     <t>IDN</t>
   </si>
   <si>
-    <t>w610198177-275</t>
-  </si>
-  <si>
-    <t>at grid node - w610198177-275</t>
+    <t>w610198177-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w610198177-275_IDN</t>
   </si>
   <si>
     <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
   </si>
   <si>
-    <t>w544403426-230</t>
-  </si>
-  <si>
-    <t>at grid node - w544403426-230</t>
-  </si>
-  <si>
-    <t>w721685825-275</t>
-  </si>
-  <si>
-    <t>at grid node - w721685825-275</t>
-  </si>
-  <si>
-    <t>w615581232-275</t>
-  </si>
-  <si>
-    <t>at grid node - w615581232-275</t>
-  </si>
-  <si>
-    <t>ID2-275</t>
-  </si>
-  <si>
-    <t>at grid node - ID2-275</t>
-  </si>
-  <si>
-    <t>ID38-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID38-500</t>
-  </si>
-  <si>
-    <t>w337039411-275</t>
-  </si>
-  <si>
-    <t>at grid node - w337039411-275</t>
-  </si>
-  <si>
-    <t>w340205049-275</t>
-  </si>
-  <si>
-    <t>at grid node - w340205049-275</t>
-  </si>
-  <si>
-    <t>ID12-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID12-500</t>
-  </si>
-  <si>
-    <t>w340978681-500</t>
-  </si>
-  <si>
-    <t>at grid node - w340978681-500</t>
-  </si>
-  <si>
-    <t>ID34-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID34-500</t>
-  </si>
-  <si>
-    <t>w960747902-500</t>
-  </si>
-  <si>
-    <t>at grid node - w960747902-500</t>
-  </si>
-  <si>
-    <t>w562061281-275</t>
-  </si>
-  <si>
-    <t>at grid node - w562061281-275</t>
-  </si>
-  <si>
-    <t>ID15-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID15-500</t>
-  </si>
-  <si>
-    <t>ID13-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID13-500</t>
-  </si>
-  <si>
-    <t>ID23-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID23-500</t>
-  </si>
-  <si>
-    <t>w736595653-500</t>
-  </si>
-  <si>
-    <t>at grid node - w736595653-500</t>
-  </si>
-  <si>
-    <t>w736595653-275</t>
-  </si>
-  <si>
-    <t>at grid node - w736595653-275</t>
-  </si>
-  <si>
-    <t>ID3-275</t>
-  </si>
-  <si>
-    <t>at grid node - ID3-275</t>
-  </si>
-  <si>
-    <t>w615581270-275</t>
-  </si>
-  <si>
-    <t>at grid node - w615581270-275</t>
-  </si>
-  <si>
-    <t>w161960924-500</t>
-  </si>
-  <si>
-    <t>at grid node - w161960924-500</t>
-  </si>
-  <si>
-    <t>w166633831-500</t>
-  </si>
-  <si>
-    <t>at grid node - w166633831-500</t>
-  </si>
-  <si>
-    <t>ID14-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID14-500</t>
-  </si>
-  <si>
-    <t>w615581242-275</t>
-  </si>
-  <si>
-    <t>at grid node - w615581242-275</t>
-  </si>
-  <si>
-    <t>ID37-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID37-500</t>
-  </si>
-  <si>
-    <t>w161965853-500</t>
-  </si>
-  <si>
-    <t>at grid node - w161965853-500</t>
-  </si>
-  <si>
-    <t>ID8-275</t>
-  </si>
-  <si>
-    <t>at grid node - ID8-275</t>
-  </si>
-  <si>
-    <t>w169444592-500</t>
-  </si>
-  <si>
-    <t>at grid node - w169444592-500</t>
-  </si>
-  <si>
-    <t>ID10-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID10-500</t>
-  </si>
-  <si>
-    <t>ID11-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID11-500</t>
-  </si>
-  <si>
-    <t>ID30-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID30-500</t>
-  </si>
-  <si>
-    <t>w629512849-500</t>
-  </si>
-  <si>
-    <t>at grid node - w629512849-500</t>
-  </si>
-  <si>
-    <t>ID29-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID29-500</t>
-  </si>
-  <si>
-    <t>w1013653012-500</t>
-  </si>
-  <si>
-    <t>at grid node - w1013653012-500</t>
-  </si>
-  <si>
-    <t>ID1-275</t>
-  </si>
-  <si>
-    <t>at grid node - ID1-275</t>
-  </si>
-  <si>
-    <t>w265318414-500</t>
-  </si>
-  <si>
-    <t>at grid node - w265318414-500</t>
-  </si>
-  <si>
-    <t>w754073846-275</t>
-  </si>
-  <si>
-    <t>at grid node - w754073846-275</t>
-  </si>
-  <si>
-    <t>w943539373-500</t>
-  </si>
-  <si>
-    <t>at grid node - w943539373-500</t>
-  </si>
-  <si>
-    <t>ID27-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID27-500</t>
-  </si>
-  <si>
-    <t>w1316786278-275</t>
-  </si>
-  <si>
-    <t>at grid node - w1316786278-275</t>
-  </si>
-  <si>
-    <t>w946191122-275</t>
-  </si>
-  <si>
-    <t>at grid node - w946191122-275</t>
-  </si>
-  <si>
-    <t>w398909640-500</t>
-  </si>
-  <si>
-    <t>at grid node - w398909640-500</t>
-  </si>
-  <si>
-    <t>ID28-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID28-500</t>
-  </si>
-  <si>
-    <t>w1186182648-500</t>
-  </si>
-  <si>
-    <t>at grid node - w1186182648-500</t>
-  </si>
-  <si>
-    <t>w754178667-275</t>
-  </si>
-  <si>
-    <t>at grid node - w754178667-275</t>
+    <t>w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w544403426-230_IDN</t>
+  </si>
+  <si>
+    <t>w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w721685825-275_IDN</t>
+  </si>
+  <si>
+    <t>w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w615581232-275_IDN</t>
+  </si>
+  <si>
+    <t>ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID2-275_IDN</t>
+  </si>
+  <si>
+    <t>ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID38-500_IDN</t>
+  </si>
+  <si>
+    <t>w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w337039411-275_IDN</t>
+  </si>
+  <si>
+    <t>w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w340205049-275_IDN</t>
+  </si>
+  <si>
+    <t>ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID12-500_IDN</t>
+  </si>
+  <si>
+    <t>w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w340978681-500_IDN</t>
+  </si>
+  <si>
+    <t>ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID34-500_IDN</t>
+  </si>
+  <si>
+    <t>w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w960747902-500_IDN</t>
+  </si>
+  <si>
+    <t>w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w562061281-275_IDN</t>
+  </si>
+  <si>
+    <t>ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID15-500_IDN</t>
+  </si>
+  <si>
+    <t>ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID13-500_IDN</t>
+  </si>
+  <si>
+    <t>ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID23-500_IDN</t>
+  </si>
+  <si>
+    <t>w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w736595653-500_IDN</t>
+  </si>
+  <si>
+    <t>w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w736595653-275_IDN</t>
+  </si>
+  <si>
+    <t>ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID3-275_IDN</t>
+  </si>
+  <si>
+    <t>w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w615581270-275_IDN</t>
+  </si>
+  <si>
+    <t>w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w161960924-500_IDN</t>
+  </si>
+  <si>
+    <t>w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w166633831-500_IDN</t>
+  </si>
+  <si>
+    <t>ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID14-500_IDN</t>
+  </si>
+  <si>
+    <t>w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w615581242-275_IDN</t>
+  </si>
+  <si>
+    <t>ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID37-500_IDN</t>
+  </si>
+  <si>
+    <t>w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w161965853-500_IDN</t>
+  </si>
+  <si>
+    <t>ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID8-275_IDN</t>
+  </si>
+  <si>
+    <t>w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w169444592-500_IDN</t>
+  </si>
+  <si>
+    <t>ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID10-500_IDN</t>
+  </si>
+  <si>
+    <t>ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID11-500_IDN</t>
+  </si>
+  <si>
+    <t>ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID30-500_IDN</t>
+  </si>
+  <si>
+    <t>w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w629512849-500_IDN</t>
+  </si>
+  <si>
+    <t>ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID29-500_IDN</t>
+  </si>
+  <si>
+    <t>w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w1013653012-500_IDN</t>
+  </si>
+  <si>
+    <t>ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID1-275_IDN</t>
+  </si>
+  <si>
+    <t>w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w265318414-500_IDN</t>
+  </si>
+  <si>
+    <t>w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w754073846-275_IDN</t>
+  </si>
+  <si>
+    <t>w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w943539373-500_IDN</t>
+  </si>
+  <si>
+    <t>ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID27-500_IDN</t>
+  </si>
+  <si>
+    <t>w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w1316786278-275_IDN</t>
+  </si>
+  <si>
+    <t>w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w946191122-275_IDN</t>
+  </si>
+  <si>
+    <t>w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w398909640-500_IDN</t>
+  </si>
+  <si>
+    <t>ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID28-500_IDN</t>
+  </si>
+  <si>
+    <t>w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w1186182648-500_IDN</t>
+  </si>
+  <si>
+    <t>w754178667-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w754178667-275_IDN</t>
   </si>
   <si>
     <t>EN_Hydro_IDN-1,EN_Hydro_IDN-2,EN_Hydro_IDN-3</t>
   </si>
   <si>
-    <t>w310695690-275</t>
-  </si>
-  <si>
-    <t>at grid node - w310695690-275</t>
-  </si>
-  <si>
-    <t>w841499143-275</t>
-  </si>
-  <si>
-    <t>at grid node - w841499143-275</t>
-  </si>
-  <si>
-    <t>w721674155-275</t>
-  </si>
-  <si>
-    <t>at grid node - w721674155-275</t>
-  </si>
-  <si>
-    <t>w399100035-500</t>
-  </si>
-  <si>
-    <t>at grid node - w399100035-500</t>
-  </si>
-  <si>
-    <t>ID36-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID36-500</t>
-  </si>
-  <si>
-    <t>ID35-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID35-500</t>
-  </si>
-  <si>
-    <t>w310958602-275</t>
-  </si>
-  <si>
-    <t>at grid node - w310958602-275</t>
-  </si>
-  <si>
-    <t>ID6-275</t>
-  </si>
-  <si>
-    <t>at grid node - ID6-275</t>
-  </si>
-  <si>
-    <t>w314452486-500</t>
-  </si>
-  <si>
-    <t>at grid node - w314452486-500</t>
-  </si>
-  <si>
-    <t>w528189342-275</t>
-  </si>
-  <si>
-    <t>at grid node - w528189342-275</t>
-  </si>
-  <si>
-    <t>ID31-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID31-500</t>
-  </si>
-  <si>
-    <t>w1193553154-275</t>
-  </si>
-  <si>
-    <t>at grid node - w1193553154-275</t>
-  </si>
-  <si>
-    <t>w264550744-500</t>
-  </si>
-  <si>
-    <t>at grid node - w264550744-500</t>
-  </si>
-  <si>
-    <t>w1316876158-275</t>
-  </si>
-  <si>
-    <t>at grid node - w1316876158-275</t>
-  </si>
-  <si>
-    <t>w754178666-275</t>
-  </si>
-  <si>
-    <t>at grid node - w754178666-275</t>
-  </si>
-  <si>
-    <t>w939542521-275</t>
-  </si>
-  <si>
-    <t>at grid node - w939542521-275</t>
-  </si>
-  <si>
-    <t>w614955993-230</t>
-  </si>
-  <si>
-    <t>at grid node - w614955993-230</t>
+    <t>w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w310695690-275_IDN</t>
+  </si>
+  <si>
+    <t>w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w841499143-275_IDN</t>
+  </si>
+  <si>
+    <t>w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w721674155-275_IDN</t>
+  </si>
+  <si>
+    <t>w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w399100035-500_IDN</t>
+  </si>
+  <si>
+    <t>ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID36-500_IDN</t>
+  </si>
+  <si>
+    <t>ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID35-500_IDN</t>
+  </si>
+  <si>
+    <t>w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w310958602-275_IDN</t>
+  </si>
+  <si>
+    <t>ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID6-275_IDN</t>
+  </si>
+  <si>
+    <t>w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w314452486-500_IDN</t>
+  </si>
+  <si>
+    <t>w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w528189342-275_IDN</t>
+  </si>
+  <si>
+    <t>ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID31-500_IDN</t>
+  </si>
+  <si>
+    <t>w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w1193553154-275_IDN</t>
+  </si>
+  <si>
+    <t>w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w264550744-500_IDN</t>
+  </si>
+  <si>
+    <t>w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w1316876158-275_IDN</t>
+  </si>
+  <si>
+    <t>w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w754178666-275_IDN</t>
+  </si>
+  <si>
+    <t>w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w939542521-275_IDN</t>
+  </si>
+  <si>
+    <t>w614955993-230_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w614955993-230_IDN</t>
   </si>
   <si>
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
-    <t>w267626657-500</t>
-  </si>
-  <si>
-    <t>at grid node - w267626657-500</t>
-  </si>
-  <si>
-    <t>w931931133-275</t>
-  </si>
-  <si>
-    <t>at grid node - w931931133-275</t>
-  </si>
-  <si>
-    <t>ID33-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID33-500</t>
-  </si>
-  <si>
-    <t>w769617021-500</t>
-  </si>
-  <si>
-    <t>at grid node - w769617021-500</t>
-  </si>
-  <si>
-    <t>w1312287191-275</t>
-  </si>
-  <si>
-    <t>at grid node - w1312287191-275</t>
-  </si>
-  <si>
-    <t>w469888049-275</t>
-  </si>
-  <si>
-    <t>at grid node - w469888049-275</t>
+    <t>w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w267626657-500_IDN</t>
+  </si>
+  <si>
+    <t>w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w931931133-275_IDN</t>
+  </si>
+  <si>
+    <t>ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID33-500_IDN</t>
+  </si>
+  <si>
+    <t>w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w769617021-500_IDN</t>
+  </si>
+  <si>
+    <t>w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w1312287191-275_IDN</t>
+  </si>
+  <si>
+    <t>w469888049-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w469888049-275_IDN</t>
   </si>
   <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
-    <t>w161960933-500</t>
-  </si>
-  <si>
-    <t>at grid node - w161960933-500</t>
-  </si>
-  <si>
-    <t>w264410236-500</t>
-  </si>
-  <si>
-    <t>at grid node - w264410236-500</t>
-  </si>
-  <si>
-    <t>w271376037-500</t>
-  </si>
-  <si>
-    <t>at grid node - w271376037-500</t>
-  </si>
-  <si>
-    <t>w604684007-500</t>
-  </si>
-  <si>
-    <t>at grid node - w604684007-500</t>
-  </si>
-  <si>
-    <t>ID17-500</t>
-  </si>
-  <si>
-    <t>at grid node - ID17-500</t>
+    <t>w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w161960933-500_IDN</t>
+  </si>
+  <si>
+    <t>w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w264410236-500_IDN</t>
+  </si>
+  <si>
+    <t>w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w271376037-500_IDN</t>
+  </si>
+  <si>
+    <t>w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w604684007-500_IDN</t>
+  </si>
+  <si>
+    <t>ID17-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - ID17-500_IDN</t>
   </si>
 </sst>
 </file>

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF14A68A-B8C9-4652-B108-7BC76F1DEDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5245ED46-2255-4607-92D0-C8FD6B424455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="927" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="236">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -721,37 +721,31 @@
     <t>at grid node - w469888049-275_IDN</t>
   </si>
   <si>
+    <t>w926254403-500_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w926254403-500_IDN</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
-    <t>w161960933-500_IDN</t>
-  </si>
-  <si>
-    <t>at grid node - w161960933-500_IDN</t>
-  </si>
-  <si>
-    <t>w264410236-500_IDN</t>
-  </si>
-  <si>
-    <t>at grid node - w264410236-500_IDN</t>
-  </si>
-  <si>
-    <t>w271376037-500_IDN</t>
-  </si>
-  <si>
-    <t>at grid node - w271376037-500_IDN</t>
-  </si>
-  <si>
-    <t>w604684007-500_IDN</t>
-  </si>
-  <si>
-    <t>at grid node - w604684007-500_IDN</t>
-  </si>
-  <si>
-    <t>ID17-500_IDN</t>
-  </si>
-  <si>
-    <t>at grid node - ID17-500_IDN</t>
+    <t>w931931121-275_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w931931121-275_IDN</t>
+  </si>
+  <si>
+    <t>w614955990-230_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w614955990-230_IDN</t>
+  </si>
+  <si>
+    <t>w759130125-230_IDN</t>
+  </si>
+  <si>
+    <t>at grid node - w759130125-230_IDN</t>
   </si>
 </sst>
 </file>
@@ -1208,13 +1202,13 @@
         <v>87</v>
       </c>
       <c r="R11" t="s">
-        <v>129</v>
+        <v>227</v>
       </c>
       <c r="S11" t="s">
-        <v>130</v>
+        <v>228</v>
       </c>
       <c r="T11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -1258,13 +1252,13 @@
         <v>87</v>
       </c>
       <c r="R12" t="s">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="S12" t="s">
+        <v>172</v>
+      </c>
+      <c r="T12" t="s">
         <v>229</v>
-      </c>
-      <c r="T12" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -1308,13 +1302,13 @@
         <v>87</v>
       </c>
       <c r="R13" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="S13" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="T13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -1364,7 +1358,7 @@
         <v>231</v>
       </c>
       <c r="T14" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -1408,13 +1402,13 @@
         <v>87</v>
       </c>
       <c r="R15" t="s">
-        <v>232</v>
+        <v>121</v>
       </c>
       <c r="S15" t="s">
-        <v>233</v>
+        <v>122</v>
       </c>
       <c r="T15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -1458,13 +1452,13 @@
         <v>87</v>
       </c>
       <c r="R16" t="s">
-        <v>234</v>
+        <v>127</v>
       </c>
       <c r="S16" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="T16" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -1508,13 +1502,13 @@
         <v>87</v>
       </c>
       <c r="R17" t="s">
-        <v>188</v>
+        <v>95</v>
       </c>
       <c r="S17" t="s">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="T17" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -1558,13 +1552,13 @@
         <v>87</v>
       </c>
       <c r="R18" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="S18" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="T18" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -1608,13 +1602,13 @@
         <v>87</v>
       </c>
       <c r="R19" t="s">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="S19" t="s">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="T19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -1658,13 +1652,13 @@
         <v>87</v>
       </c>
       <c r="R20" t="s">
-        <v>236</v>
+        <v>113</v>
       </c>
       <c r="S20" t="s">
-        <v>237</v>
+        <v>114</v>
       </c>
       <c r="T20" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
@@ -1704,6 +1698,18 @@
       <c r="O21" t="s">
         <v>214</v>
       </c>
+      <c r="Q21" t="s">
+        <v>87</v>
+      </c>
+      <c r="R21" t="s">
+        <v>202</v>
+      </c>
+      <c r="S21" t="s">
+        <v>203</v>
+      </c>
+      <c r="T21" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
@@ -1742,6 +1748,18 @@
       <c r="O22" t="s">
         <v>214</v>
       </c>
+      <c r="Q22" t="s">
+        <v>87</v>
+      </c>
+      <c r="R22" t="s">
+        <v>212</v>
+      </c>
+      <c r="S22" t="s">
+        <v>213</v>
+      </c>
+      <c r="T22" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
@@ -1780,6 +1798,18 @@
       <c r="O23" t="s">
         <v>214</v>
       </c>
+      <c r="Q23" t="s">
+        <v>87</v>
+      </c>
+      <c r="R23" t="s">
+        <v>232</v>
+      </c>
+      <c r="S23" t="s">
+        <v>233</v>
+      </c>
+      <c r="T23" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
@@ -1817,6 +1847,18 @@
       </c>
       <c r="O24" t="s">
         <v>214</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>87</v>
+      </c>
+      <c r="R24" t="s">
+        <v>234</v>
+      </c>
+      <c r="S24" t="s">
+        <v>235</v>
+      </c>
+      <c r="T24" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">

--- a/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_IDN_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5245ED46-2255-4607-92D0-C8FD6B424455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C501738-90C6-4FFA-9BE2-DB32E25D598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
